--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/feature_importance.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/feature_importance.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.166754478221572</v>
+        <v>0.154302547196298</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1504608060444715</v>
+        <v>0.1528519035445194</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -514,11 +514,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1385703926872391</v>
+        <v>0.1403942819754556</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -537,11 +537,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1362914619065732</v>
+        <v>0.1397844713476928</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1353084398450718</v>
+        <v>0.1286252384640951</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1221422130726932</v>
+        <v>0.1284604977443455</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -606,11 +606,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1208818624175318</v>
+        <v>0.1222966270226446</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02959034580484736</v>
+        <v>0.03328443270494898</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1750392083298654</v>
+        <v>0.156376594392571</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -675,11 +675,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1391854057821905</v>
+        <v>0.1439867631950493</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1336452624054455</v>
+        <v>0.1414027824361898</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -721,11 +721,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1313540924111277</v>
+        <v>0.1371781355884573</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1311058751338119</v>
+        <v>0.1339974284758998</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
@@ -767,11 +767,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1307609839187382</v>
+        <v>0.133418717631025</v>
       </c>
       <c r="E15" t="n">
         <v>6</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1259518155208145</v>
+        <v>0.1196501409149371</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.03295735649800619</v>
+        <v>0.03398943736587071</v>
       </c>
       <c r="E17" t="n">
         <v>8</v>
@@ -836,11 +836,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1615434309580455</v>
+        <v>0.147515215313564</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -859,11 +859,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.1456044980574699</v>
+        <v>0.1451902563576697</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -882,11 +882,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1413895803599578</v>
+        <v>0.1419160104202251</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -905,11 +905,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1365575121359089</v>
+        <v>0.1382307877672211</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -928,11 +928,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1338840303210592</v>
+        <v>0.1344338888179762</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
@@ -951,11 +951,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1235486524962631</v>
+        <v>0.1288227005218545</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1172181361484257</v>
+        <v>0.1233443676160132</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.04025415952286986</v>
+        <v>0.04054677318547623</v>
       </c>
       <c r="E25" t="n">
         <v>8</v>
@@ -1020,11 +1020,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.1469942778243226</v>
+        <v>0.1456517975149239</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1043,11 +1043,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1450076649591867</v>
+        <v>0.142337706210858</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -1066,11 +1066,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1421839823812669</v>
+        <v>0.1419412301064401</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1370933230080427</v>
+        <v>0.1390930183783458</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1337151567182394</v>
+        <v>0.1377905410438204</v>
       </c>
       <c r="E30" t="n">
         <v>5</v>
@@ -1135,11 +1135,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1313882358879054</v>
+        <v>0.1306796267971169</v>
       </c>
       <c r="E31" t="n">
         <v>6</v>
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1249241073532954</v>
+        <v>0.1228270206019691</v>
       </c>
       <c r="E32" t="n">
         <v>7</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.03869325186774095</v>
+        <v>0.03967905934652591</v>
       </c>
       <c r="E33" t="n">
         <v>8</v>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1539018391354902</v>
+        <v>0.1644723132958532</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1406845202786054</v>
+        <v>0.1426364455374047</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1250,11 +1250,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1360966315280443</v>
+        <v>0.1348859527199933</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
@@ -1273,11 +1273,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1358267464414914</v>
+        <v>0.1326098340965588</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1326539072388789</v>
+        <v>0.1299660916429884</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
@@ -1319,11 +1319,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1304184077306715</v>
+        <v>0.128985313655194</v>
       </c>
       <c r="E39" t="n">
         <v>6</v>
@@ -1342,11 +1342,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.1292872666449223</v>
+        <v>0.1288525876530247</v>
       </c>
       <c r="E40" t="n">
         <v>7</v>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.0411306810018962</v>
+        <v>0.03759146139898294</v>
       </c>
       <c r="E41" t="n">
         <v>8</v>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1507784783512724</v>
+        <v>0.1582355616342049</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.150640682587615</v>
+        <v>0.1499463744708696</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1434,11 +1434,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.1440181593006969</v>
+        <v>0.1376463622511958</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
@@ -1457,11 +1457,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.1407743762896062</v>
+        <v>0.1366350112350373</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.1357075601375815</v>
+        <v>0.136466312762777</v>
       </c>
       <c r="E46" t="n">
         <v>5</v>
@@ -1503,11 +1503,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.1295568120214087</v>
+        <v>0.128607544577936</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1229739233232421</v>
+        <v>0.1284436812795852</v>
       </c>
       <c r="E48" t="n">
         <v>7</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.02555000798857728</v>
+        <v>0.0240191517883942</v>
       </c>
       <c r="E49" t="n">
         <v>8</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.1666568725148211</v>
+        <v>0.151966046643596</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.1406347300554191</v>
+        <v>0.142690005352972</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1618,11 +1618,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.1381308573111526</v>
+        <v>0.1397099325973546</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.1342609369640257</v>
+        <v>0.1360014658128501</v>
       </c>
       <c r="E53" t="n">
         <v>4</v>
@@ -1664,11 +1664,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.132906554066411</v>
+        <v>0.131873005931816</v>
       </c>
       <c r="E54" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.127941775683174</v>
+        <v>0.1308321693073924</v>
       </c>
       <c r="E55" t="n">
         <v>6</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1248623050143599</v>
+        <v>0.1304157650141719</v>
       </c>
       <c r="E56" t="n">
         <v>7</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.03460596839063654</v>
+        <v>0.03651160933984708</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.1608969971318128</v>
+        <v>0.1653523498251288</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.1452878432938741</v>
+        <v>0.1465361942559615</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.1420821317073041</v>
+        <v>0.1443178594227829</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
@@ -1825,11 +1825,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.1389454969261719</v>
+        <v>0.1298587322517364</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.1328925633549984</v>
+        <v>0.1294649911294196</v>
       </c>
       <c r="E62" t="n">
         <v>5</v>
@@ -1871,11 +1871,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.1279118716460156</v>
+        <v>0.1270891467301264</v>
       </c>
       <c r="E63" t="n">
         <v>6</v>
@@ -1894,11 +1894,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.126686253902498</v>
+        <v>0.1265563871228574</v>
       </c>
       <c r="E64" t="n">
         <v>7</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.02529684203732511</v>
+        <v>0.03082433926198718</v>
       </c>
       <c r="E65" t="n">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.1540470577757507</v>
+        <v>0.1559057778329406</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.143486293793166</v>
+        <v>0.1454531137091826</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.140310891879209</v>
+        <v>0.1406655059016547</v>
       </c>
       <c r="E68" t="n">
         <v>3</v>
@@ -2009,11 +2009,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.1385384093872809</v>
+        <v>0.1329748557986172</v>
       </c>
       <c r="E69" t="n">
         <v>4</v>
@@ -2032,11 +2032,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.13255964757731</v>
+        <v>0.1327427776790268</v>
       </c>
       <c r="E70" t="n">
         <v>5</v>
@@ -2055,11 +2055,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.1264204965484631</v>
+        <v>0.1303346588555906</v>
       </c>
       <c r="E71" t="n">
         <v>6</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.1253163263402564</v>
+        <v>0.1269161101279769</v>
       </c>
       <c r="E72" t="n">
         <v>7</v>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.03932087669856386</v>
+        <v>0.03500720009501071</v>
       </c>
       <c r="E73" t="n">
         <v>8</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.1605640408199236</v>
+        <v>0.151058511953328</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.146881718781076</v>
+        <v>0.1466215281307219</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.1467656947634328</v>
+        <v>0.1447971415890213</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
@@ -2193,11 +2193,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.1350304743135298</v>
+        <v>0.1390650831813405</v>
       </c>
       <c r="E77" t="n">
         <v>4</v>
@@ -2216,11 +2216,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.1320520596772956</v>
+        <v>0.1274185224007021</v>
       </c>
       <c r="E78" t="n">
         <v>5</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.1214695613051114</v>
+        <v>0.1264478742460799</v>
       </c>
       <c r="E79" t="n">
         <v>6</v>
@@ -2262,11 +2262,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.1184166375407022</v>
+        <v>0.1226405460861415</v>
       </c>
       <c r="E80" t="n">
         <v>7</v>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.03881981279892857</v>
+        <v>0.04195079241266478</v>
       </c>
       <c r="E81" t="n">
         <v>8</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.1541881133878216</v>
+        <v>0.1452802570235586</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.1436365063208493</v>
+        <v>0.1414037724313587</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -2354,11 +2354,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.1399881293677699</v>
+        <v>0.13637084083502</v>
       </c>
       <c r="E84" t="n">
         <v>3</v>
@@ -2377,11 +2377,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.1390676792807275</v>
+        <v>0.1361004323993872</v>
       </c>
       <c r="E85" t="n">
         <v>4</v>
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.1381784978057453</v>
+        <v>0.1358016022569452</v>
       </c>
       <c r="E86" t="n">
         <v>5</v>
@@ -2423,11 +2423,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1303351450390472</v>
+        <v>0.1336960669577834</v>
       </c>
       <c r="E87" t="n">
         <v>6</v>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.1170592834968054</v>
+        <v>0.1330443273179017</v>
       </c>
       <c r="E88" t="n">
         <v>7</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.0375466453012339</v>
+        <v>0.03830270077804536</v>
       </c>
       <c r="E89" t="n">
         <v>8</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.1724525874473294</v>
+        <v>0.1645700749107897</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.1614057464352459</v>
+        <v>0.1485477537956983</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -2538,11 +2538,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.1333149032409882</v>
+        <v>0.1442978959435175</v>
       </c>
       <c r="E92" t="n">
         <v>3</v>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1312893395487455</v>
+        <v>0.1327889229323627</v>
       </c>
       <c r="E93" t="n">
         <v>4</v>
@@ -2584,11 +2584,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.1276758339791461</v>
+        <v>0.1266278834966023</v>
       </c>
       <c r="E94" t="n">
         <v>5</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.1226228612514303</v>
+        <v>0.1254527397281436</v>
       </c>
       <c r="E95" t="n">
         <v>6</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.119864681738801</v>
+        <v>0.1207095002717092</v>
       </c>
       <c r="E96" t="n">
         <v>7</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.03137404635831371</v>
+        <v>0.03700522892117672</v>
       </c>
       <c r="E97" t="n">
         <v>8</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.1586690174594589</v>
+        <v>0.149965430738608</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -2699,11 +2699,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.1408867262754463</v>
+        <v>0.1407228413973617</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -2722,11 +2722,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.1403299609905801</v>
+        <v>0.1368219343334864</v>
       </c>
       <c r="E100" t="n">
         <v>3</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.1325562370409011</v>
+        <v>0.1352904423817149</v>
       </c>
       <c r="E101" t="n">
         <v>4</v>
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.1323205105097069</v>
+        <v>0.133279358928666</v>
       </c>
       <c r="E102" t="n">
         <v>5</v>
@@ -2791,11 +2791,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.1312459616824921</v>
+        <v>0.1322783090418201</v>
       </c>
       <c r="E103" t="n">
         <v>6</v>
@@ -2814,11 +2814,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.1269685481061845</v>
+        <v>0.1297544573980479</v>
       </c>
       <c r="E104" t="n">
         <v>7</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.03702303793523013</v>
+        <v>0.04188722578029498</v>
       </c>
       <c r="E105" t="n">
         <v>8</v>
@@ -2860,11 +2860,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.1540095354726442</v>
+        <v>0.1488443327461026</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.1496140424630082</v>
+        <v>0.1469151406445519</v>
       </c>
       <c r="E107" t="n">
         <v>2</v>
@@ -2906,11 +2906,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.1384445851358713</v>
+        <v>0.1427601716424594</v>
       </c>
       <c r="E108" t="n">
         <v>3</v>
@@ -2929,11 +2929,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.1367953233392926</v>
+        <v>0.1423385683316135</v>
       </c>
       <c r="E109" t="n">
         <v>4</v>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.1317874668786071</v>
+        <v>0.1374766550033443</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -2975,11 +2975,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.1309738370408502</v>
+        <v>0.1275702533608491</v>
       </c>
       <c r="E111" t="n">
         <v>6</v>
@@ -2998,11 +2998,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.1263958328927171</v>
+        <v>0.1229167353446122</v>
       </c>
       <c r="E112" t="n">
         <v>7</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.03197937677700926</v>
+        <v>0.03117814292646691</v>
       </c>
       <c r="E113" t="n">
         <v>8</v>
@@ -3044,11 +3044,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.1489653337645632</v>
+        <v>0.1512893293587264</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3067,11 +3067,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.1471404683070491</v>
+        <v>0.1450671581513042</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.1392370181498083</v>
+        <v>0.1403905318574988</v>
       </c>
       <c r="E116" t="n">
         <v>3</v>
@@ -3113,11 +3113,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1375093620442624</v>
+        <v>0.1396039118053769</v>
       </c>
       <c r="E117" t="n">
         <v>4</v>
@@ -3136,11 +3136,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.1326726436599781</v>
+        <v>0.1313995559608319</v>
       </c>
       <c r="E118" t="n">
         <v>5</v>
@@ -3159,11 +3159,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.1312058176380994</v>
+        <v>0.1305120804206972</v>
       </c>
       <c r="E119" t="n">
         <v>6</v>
@@ -3182,11 +3182,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.1267140648959282</v>
+        <v>0.1285743115230352</v>
       </c>
       <c r="E120" t="n">
         <v>7</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.03655529154031134</v>
+        <v>0.03316312092252931</v>
       </c>
       <c r="E121" t="n">
         <v>8</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.1516035561058999</v>
+        <v>0.1586560731382151</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.1494543422040168</v>
+        <v>0.1431104166631328</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.1406436149554991</v>
+        <v>0.1401647397759969</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
@@ -3297,11 +3297,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.1397310889713893</v>
+        <v>0.1377806096579051</v>
       </c>
       <c r="E125" t="n">
         <v>4</v>
@@ -3320,11 +3320,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.1383120715752993</v>
+        <v>0.1341992597046637</v>
       </c>
       <c r="E126" t="n">
         <v>5</v>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.1260768612534578</v>
+        <v>0.1289097127788769</v>
       </c>
       <c r="E127" t="n">
         <v>6</v>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.1248681352546777</v>
+        <v>0.1198121094461994</v>
       </c>
       <c r="E128" t="n">
         <v>7</v>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.02931032967976001</v>
+        <v>0.03736707883501005</v>
       </c>
       <c r="E129" t="n">
         <v>8</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.1475917128710594</v>
+        <v>0.1498991259733833</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -3435,11 +3435,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.1419530849516517</v>
+        <v>0.1486597199238371</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.1413132605148232</v>
+        <v>0.1459530632865069</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.1398429414020549</v>
+        <v>0.1427667476111797</v>
       </c>
       <c r="E133" t="n">
         <v>4</v>
@@ -3504,11 +3504,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.1366654814807637</v>
+        <v>0.1288329930949922</v>
       </c>
       <c r="E134" t="n">
         <v>5</v>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.1338364809299779</v>
+        <v>0.125466819632721</v>
       </c>
       <c r="E135" t="n">
         <v>6</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.1291579072136389</v>
+        <v>0.1254164343351368</v>
       </c>
       <c r="E136" t="n">
         <v>7</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.02963913063603039</v>
+        <v>0.03300509614224292</v>
       </c>
       <c r="E137" t="n">
         <v>8</v>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.1734640320746739</v>
+        <v>0.1594405556880039</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.1499776878717295</v>
+        <v>0.1509276592081818</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -3642,11 +3642,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.1409805276916304</v>
+        <v>0.1395563231779339</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.1347377380365428</v>
+        <v>0.1373352187844752</v>
       </c>
       <c r="E141" t="n">
         <v>4</v>
@@ -3688,11 +3688,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.1252521768834684</v>
+        <v>0.1290814860834939</v>
       </c>
       <c r="E142" t="n">
         <v>5</v>
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.1241411234479632</v>
+        <v>0.1244802891144763</v>
       </c>
       <c r="E143" t="n">
         <v>6</v>
@@ -3734,11 +3734,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.1174390089299801</v>
+        <v>0.1239075496315486</v>
       </c>
       <c r="E144" t="n">
         <v>7</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.03400770506401182</v>
+        <v>0.03527091831188647</v>
       </c>
       <c r="E145" t="n">
         <v>8</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.1469126294681928</v>
+        <v>0.1538892887108169</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.143752671393584</v>
+        <v>0.1477428456466797</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -3826,11 +3826,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.1380506373432278</v>
+        <v>0.1401575929763592</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.1361040380527976</v>
+        <v>0.1348435948598587</v>
       </c>
       <c r="E149" t="n">
         <v>4</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.1332164035361633</v>
+        <v>0.1333280557716052</v>
       </c>
       <c r="E150" t="n">
         <v>5</v>
@@ -3895,11 +3895,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.1320361782688053</v>
+        <v>0.1303859441961586</v>
       </c>
       <c r="E151" t="n">
         <v>6</v>
@@ -3918,11 +3918,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.1280800520219542</v>
+        <v>0.1198436748477982</v>
       </c>
       <c r="E152" t="n">
         <v>7</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.0418473899152751</v>
+        <v>0.03980900299072353</v>
       </c>
       <c r="E153" t="n">
         <v>8</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.1688294095120784</v>
+        <v>0.1554617319292695</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.1579101205780468</v>
+        <v>0.1494907432218062</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4010,11 +4010,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.1316036114079206</v>
+        <v>0.1432700551417849</v>
       </c>
       <c r="E156" t="n">
         <v>3</v>
@@ -4033,11 +4033,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.1298245279159387</v>
+        <v>0.141388161569878</v>
       </c>
       <c r="E157" t="n">
         <v>4</v>
@@ -4056,11 +4056,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.1283126646160228</v>
+        <v>0.1346612212479905</v>
       </c>
       <c r="E158" t="n">
         <v>5</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.1282762129343632</v>
+        <v>0.1251173606433073</v>
       </c>
       <c r="E159" t="n">
         <v>6</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.1202891017919093</v>
+        <v>0.1159835094186648</v>
       </c>
       <c r="E160" t="n">
         <v>7</v>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.03495435124372032</v>
+        <v>0.03462721682729877</v>
       </c>
       <c r="E161" t="n">
         <v>8</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.1593344978022734</v>
+        <v>0.1621265897738878</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.1520806433217733</v>
+        <v>0.1395953532130492</v>
       </c>
       <c r="E163" t="n">
         <v>2</v>
@@ -4194,11 +4194,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.1385516023423299</v>
+        <v>0.1375601025409012</v>
       </c>
       <c r="E164" t="n">
         <v>3</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.1366853625221946</v>
+        <v>0.1347370233356243</v>
       </c>
       <c r="E165" t="n">
         <v>4</v>
@@ -4240,11 +4240,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.1266851499106459</v>
+        <v>0.1311129393316219</v>
       </c>
       <c r="E166" t="n">
         <v>5</v>
@@ -4263,11 +4263,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.1262544603621953</v>
+        <v>0.1292333775029879</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -4286,11 +4286,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.1222624497614324</v>
+        <v>0.1281748692707932</v>
       </c>
       <c r="E168" t="n">
         <v>7</v>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.03814583397715519</v>
+        <v>0.03745974503113442</v>
       </c>
       <c r="E169" t="n">
         <v>8</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.1601909869000728</v>
+        <v>0.156096636722261</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -4355,11 +4355,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.1421490917259413</v>
+        <v>0.1416058943890222</v>
       </c>
       <c r="E171" t="n">
         <v>2</v>
@@ -4378,11 +4378,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.1374700310452308</v>
+        <v>0.1347177569925307</v>
       </c>
       <c r="E172" t="n">
         <v>3</v>
@@ -4401,11 +4401,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.1363794196228638</v>
+        <v>0.1340045737823266</v>
       </c>
       <c r="E173" t="n">
         <v>4</v>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.1337169098847794</v>
+        <v>0.133620635599935</v>
       </c>
       <c r="E174" t="n">
         <v>5</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.1312184568762555</v>
+        <v>0.1295829705330463</v>
       </c>
       <c r="E175" t="n">
         <v>6</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.1200220805292751</v>
+        <v>0.1287662943770966</v>
       </c>
       <c r="E176" t="n">
         <v>7</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.03885302341558146</v>
+        <v>0.04160523760378185</v>
       </c>
       <c r="E177" t="n">
         <v>8</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.1487447892060389</v>
+        <v>0.150012559438695</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -4539,11 +4539,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.1481468065376285</v>
+        <v>0.1493112485309464</v>
       </c>
       <c r="E179" t="n">
         <v>2</v>
@@ -4562,11 +4562,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.1382875826591335</v>
+        <v>0.1394143037889071</v>
       </c>
       <c r="E180" t="n">
         <v>3</v>
@@ -4585,11 +4585,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.1370114767829118</v>
+        <v>0.13733577455974</v>
       </c>
       <c r="E181" t="n">
         <v>4</v>
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.1366170085279404</v>
+        <v>0.1330852625139635</v>
       </c>
       <c r="E182" t="n">
         <v>5</v>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.1338454692139527</v>
+        <v>0.1267388423475976</v>
       </c>
       <c r="E183" t="n">
         <v>6</v>
@@ -4654,11 +4654,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.1255246749297788</v>
+        <v>0.1256788037451647</v>
       </c>
       <c r="E184" t="n">
         <v>7</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.03182219214261535</v>
+        <v>0.03842320507498571</v>
       </c>
       <c r="E185" t="n">
         <v>8</v>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.1557646206679608</v>
+        <v>0.1515395151341888</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.1554178167303918</v>
+        <v>0.1472873058936272</v>
       </c>
       <c r="E187" t="n">
         <v>2</v>
@@ -4746,11 +4746,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.1417778683459959</v>
+        <v>0.1389934096528141</v>
       </c>
       <c r="E188" t="n">
         <v>3</v>
@@ -4769,11 +4769,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.136792848627606</v>
+        <v>0.1388652290585153</v>
       </c>
       <c r="E189" t="n">
         <v>4</v>
@@ -4792,11 +4792,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.1312565769932766</v>
+        <v>0.1348342557711407</v>
       </c>
       <c r="E190" t="n">
         <v>5</v>
@@ -4815,11 +4815,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.1309066954899983</v>
+        <v>0.1266224970350049</v>
       </c>
       <c r="E191" t="n">
         <v>6</v>
@@ -4838,11 +4838,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.1231901241513838</v>
+        <v>0.1248673439646107</v>
       </c>
       <c r="E192" t="n">
         <v>7</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.02489344899338679</v>
+        <v>0.03699044349009837</v>
       </c>
       <c r="E193" t="n">
         <v>8</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.1670212648937824</v>
+        <v>0.162995294493098</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.146128839374799</v>
+        <v>0.1600763857508695</v>
       </c>
       <c r="E195" t="n">
         <v>2</v>
@@ -4930,11 +4930,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.1320179507373282</v>
+        <v>0.1382130335238512</v>
       </c>
       <c r="E196" t="n">
         <v>3</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.1301606335377061</v>
+        <v>0.1310668062159561</v>
       </c>
       <c r="E197" t="n">
         <v>4</v>
@@ -4976,11 +4976,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.1293384768832795</v>
+        <v>0.1250186320325852</v>
       </c>
       <c r="E198" t="n">
         <v>5</v>
@@ -4999,11 +4999,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.1213592250929973</v>
+        <v>0.118122235135285</v>
       </c>
       <c r="E199" t="n">
         <v>6</v>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.1130263995009727</v>
+        <v>0.1112509182229281</v>
       </c>
       <c r="E200" t="n">
         <v>7</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.06094720997913503</v>
+        <v>0.05325669462542693</v>
       </c>
       <c r="E201" t="n">
         <v>8</v>
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.160271276894365</v>
+        <v>0.1578908535418077</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
@@ -5091,11 +5091,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.1588112648117641</v>
+        <v>0.1533512776210923</v>
       </c>
       <c r="E203" t="n">
         <v>2</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.134239544684099</v>
+        <v>0.1425578351985253</v>
       </c>
       <c r="E204" t="n">
         <v>3</v>
@@ -5137,11 +5137,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.1322739696166887</v>
+        <v>0.1360599311920153</v>
       </c>
       <c r="E205" t="n">
         <v>4</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.1284173991916969</v>
+        <v>0.1354066313816033</v>
       </c>
       <c r="E206" t="n">
         <v>5</v>
@@ -5183,11 +5183,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.1249243546061934</v>
+        <v>0.1285877237613569</v>
       </c>
       <c r="E207" t="n">
         <v>6</v>
@@ -5206,11 +5206,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.115664581091453</v>
+        <v>0.1156552694358485</v>
       </c>
       <c r="E208" t="n">
         <v>7</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.04539760910373975</v>
+        <v>0.03049047786775073</v>
       </c>
       <c r="E209" t="n">
         <v>8</v>
@@ -5252,11 +5252,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.1573615280668692</v>
+        <v>0.1590698535013453</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
@@ -5275,11 +5275,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.1515452294748202</v>
+        <v>0.1504471572042734</v>
       </c>
       <c r="E211" t="n">
         <v>2</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.1352637681178734</v>
+        <v>0.1461149692747995</v>
       </c>
       <c r="E212" t="n">
         <v>3</v>
@@ -5321,11 +5321,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.1346531362089396</v>
+        <v>0.1386347086036663</v>
       </c>
       <c r="E213" t="n">
         <v>4</v>
@@ -5344,11 +5344,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.1331516732552368</v>
+        <v>0.1289009549323515</v>
       </c>
       <c r="E214" t="n">
         <v>5</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.130460030510802</v>
+        <v>0.1238083949388272</v>
       </c>
       <c r="E215" t="n">
         <v>6</v>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.1256514926399811</v>
+        <v>0.1226841174096568</v>
       </c>
       <c r="E216" t="n">
         <v>7</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.0319131417254777</v>
+        <v>0.03033984413508006</v>
       </c>
       <c r="E217" t="n">
         <v>8</v>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.1546248308414427</v>
+        <v>0.1654255045657358</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -5459,11 +5459,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.1464596236184363</v>
+        <v>0.1411387772047096</v>
       </c>
       <c r="E219" t="n">
         <v>2</v>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.1433017600787712</v>
+        <v>0.1384400022974987</v>
       </c>
       <c r="E220" t="n">
         <v>3</v>
@@ -5505,11 +5505,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.138425845689629</v>
+        <v>0.1356918316308572</v>
       </c>
       <c r="E221" t="n">
         <v>4</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.1248024472724092</v>
+        <v>0.1266438223119609</v>
       </c>
       <c r="E222" t="n">
         <v>5</v>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.1237723448598496</v>
+        <v>0.1265064090650771</v>
       </c>
       <c r="E223" t="n">
         <v>6</v>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.119880124339266</v>
+        <v>0.1227429916512558</v>
       </c>
       <c r="E224" t="n">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.04873302330019611</v>
+        <v>0.04341066127290499</v>
       </c>
       <c r="E225" t="n">
         <v>8</v>
@@ -5620,11 +5620,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.1632939342843895</v>
+        <v>0.175575704624629</v>
       </c>
       <c r="E226" t="n">
         <v>1</v>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.1594579883006571</v>
+        <v>0.1384862950187959</v>
       </c>
       <c r="E227" t="n">
         <v>2</v>
@@ -5666,11 +5666,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.1366687067642741</v>
+        <v>0.1377158003601706</v>
       </c>
       <c r="E228" t="n">
         <v>3</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.134620088307622</v>
+        <v>0.1288304476021281</v>
       </c>
       <c r="E229" t="n">
         <v>4</v>
@@ -5712,11 +5712,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.1271570796624333</v>
+        <v>0.1286891493745462</v>
       </c>
       <c r="E230" t="n">
         <v>5</v>
@@ -5735,11 +5735,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.1249682792855795</v>
+        <v>0.1274845653166451</v>
       </c>
       <c r="E231" t="n">
         <v>6</v>
@@ -5758,11 +5758,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.1232016109435718</v>
+        <v>0.1269503582864104</v>
       </c>
       <c r="E232" t="n">
         <v>7</v>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.03063231245147267</v>
+        <v>0.03626767941667489</v>
       </c>
       <c r="E233" t="n">
         <v>8</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.1733818332768428</v>
+        <v>0.1644936083843054</v>
       </c>
       <c r="E234" t="n">
         <v>1</v>
@@ -5827,11 +5827,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.1520418805831783</v>
+        <v>0.1597104575828431</v>
       </c>
       <c r="E235" t="n">
         <v>2</v>
@@ -5850,11 +5850,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.145626924849412</v>
+        <v>0.1474661494666263</v>
       </c>
       <c r="E236" t="n">
         <v>3</v>
@@ -5873,11 +5873,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.1314551923127469</v>
+        <v>0.1449521999380427</v>
       </c>
       <c r="E237" t="n">
         <v>4</v>
@@ -5896,11 +5896,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.1300103319653787</v>
+        <v>0.1242367343453318</v>
       </c>
       <c r="E238" t="n">
         <v>5</v>
@@ -5919,11 +5919,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.1292320544804382</v>
+        <v>0.1111483899255506</v>
       </c>
       <c r="E239" t="n">
         <v>6</v>
@@ -5942,11 +5942,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.105341476014735</v>
+        <v>0.1065668500387854</v>
       </c>
       <c r="E240" t="n">
         <v>7</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.03291030651726813</v>
+        <v>0.04142561031851472</v>
       </c>
       <c r="E241" t="n">
         <v>8</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.1753688720402702</v>
+        <v>0.1634285959043757</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
@@ -6011,11 +6011,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.1430352781929868</v>
+        <v>0.1521960866550572</v>
       </c>
       <c r="E243" t="n">
         <v>2</v>
@@ -6034,11 +6034,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.1414827646879273</v>
+        <v>0.140185493775821</v>
       </c>
       <c r="E244" t="n">
         <v>3</v>
@@ -6057,11 +6057,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.1333402316851078</v>
+        <v>0.1397425880553694</v>
       </c>
       <c r="E245" t="n">
         <v>4</v>
@@ -6080,11 +6080,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.130977984134236</v>
+        <v>0.1296235904537795</v>
       </c>
       <c r="E246" t="n">
         <v>5</v>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.1240779970744743</v>
+        <v>0.1241498488787793</v>
       </c>
       <c r="E247" t="n">
         <v>6</v>
@@ -6126,11 +6126,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.1178766940438739</v>
+        <v>0.1233432041010283</v>
       </c>
       <c r="E248" t="n">
         <v>7</v>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.03384017814112355</v>
+        <v>0.02733059217578954</v>
       </c>
       <c r="E249" t="n">
         <v>8</v>
@@ -6172,11 +6172,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.1543263702222125</v>
+        <v>0.171996073879084</v>
       </c>
       <c r="E250" t="n">
         <v>1</v>
@@ -6195,11 +6195,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.1514855824446981</v>
+        <v>0.1430351495102783</v>
       </c>
       <c r="E251" t="n">
         <v>2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.1421239437887777</v>
+        <v>0.1391227297015839</v>
       </c>
       <c r="E252" t="n">
         <v>3</v>
@@ -6241,11 +6241,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0.1332448978596311</v>
+        <v>0.1320259122968977</v>
       </c>
       <c r="E253" t="n">
         <v>4</v>
@@ -6264,11 +6264,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.1293921149219636</v>
+        <v>0.1286003178879209</v>
       </c>
       <c r="E254" t="n">
         <v>5</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.1281296693098865</v>
+        <v>0.127284086920187</v>
       </c>
       <c r="E255" t="n">
         <v>6</v>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.1230743664531718</v>
+        <v>0.1246062343665568</v>
       </c>
       <c r="E256" t="n">
         <v>7</v>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.03822305499965898</v>
+        <v>0.03332949543749153</v>
       </c>
       <c r="E257" t="n">
         <v>8</v>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.1682407298905595</v>
+        <v>0.1651365657207518</v>
       </c>
       <c r="E258" t="n">
         <v>1</v>
@@ -6379,11 +6379,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.1445781744130656</v>
+        <v>0.1572220682699843</v>
       </c>
       <c r="E259" t="n">
         <v>2</v>
@@ -6402,11 +6402,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.1395644025957396</v>
+        <v>0.1408459022532965</v>
       </c>
       <c r="E260" t="n">
         <v>3</v>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.1387845873455838</v>
+        <v>0.134788313695597</v>
       </c>
       <c r="E261" t="n">
         <v>4</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.1303380309290165</v>
+        <v>0.1329689897224196</v>
       </c>
       <c r="E262" t="n">
         <v>5</v>
@@ -6471,11 +6471,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.1216141021291574</v>
+        <v>0.120189815144286</v>
       </c>
       <c r="E263" t="n">
         <v>6</v>
@@ -6494,11 +6494,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.1197565522995585</v>
+        <v>0.116908537047925</v>
       </c>
       <c r="E264" t="n">
         <v>7</v>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.03712342039731906</v>
+        <v>0.0319398081457398</v>
       </c>
       <c r="E265" t="n">
         <v>8</v>
@@ -6540,11 +6540,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.1729821141017556</v>
+        <v>0.1641360042788341</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.1482318884008322</v>
+        <v>0.1462623283719768</v>
       </c>
       <c r="E267" t="n">
         <v>2</v>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.1445189732601044</v>
+        <v>0.132345958957445</v>
       </c>
       <c r="E268" t="n">
         <v>3</v>
@@ -6609,11 +6609,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.136904572003786</v>
+        <v>0.1319600182319249</v>
       </c>
       <c r="E269" t="n">
         <v>4</v>
@@ -6632,11 +6632,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.1359026348389884</v>
+        <v>0.1314663213189807</v>
       </c>
       <c r="E270" t="n">
         <v>5</v>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.1283719363847603</v>
+        <v>0.1310177957701777</v>
       </c>
       <c r="E271" t="n">
         <v>6</v>
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.09713812031202824</v>
+        <v>0.1282997927073372</v>
       </c>
       <c r="E272" t="n">
         <v>7</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.03594976069774482</v>
+        <v>0.0345117803633237</v>
       </c>
       <c r="E273" t="n">
         <v>8</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>0.1552991183420361</v>
+        <v>0.1612596853077023</v>
       </c>
       <c r="E274" t="n">
         <v>1</v>
@@ -6747,11 +6747,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0.1421236683860495</v>
+        <v>0.1401561638354045</v>
       </c>
       <c r="E275" t="n">
         <v>2</v>
@@ -6770,11 +6770,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0.1409723166760047</v>
+        <v>0.1360383443208569</v>
       </c>
       <c r="E276" t="n">
         <v>3</v>
@@ -6793,11 +6793,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0.1409028363885957</v>
+        <v>0.135854021621597</v>
       </c>
       <c r="E277" t="n">
         <v>4</v>
@@ -6816,11 +6816,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0.1347107327697775</v>
+        <v>0.1356572477110198</v>
       </c>
       <c r="E278" t="n">
         <v>5</v>
@@ -6839,11 +6839,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0.1269383899643912</v>
+        <v>0.1311563477071209</v>
       </c>
       <c r="E279" t="n">
         <v>6</v>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0.1260149171931695</v>
+        <v>0.1249587514575131</v>
       </c>
       <c r="E280" t="n">
         <v>7</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>0.03303802027997592</v>
+        <v>0.03491943803878578</v>
       </c>
       <c r="E281" t="n">
         <v>8</v>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>0.1633089165970898</v>
+        <v>0.1785808417698981</v>
       </c>
       <c r="E282" t="n">
         <v>1</v>
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0.1461356454915965</v>
+        <v>0.1489900530528348</v>
       </c>
       <c r="E283" t="n">
         <v>2</v>
@@ -6954,11 +6954,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0.1364361621100155</v>
+        <v>0.1377765786824574</v>
       </c>
       <c r="E284" t="n">
         <v>3</v>
@@ -6977,11 +6977,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>0.1315005210761119</v>
+        <v>0.1353089452063468</v>
       </c>
       <c r="E285" t="n">
         <v>4</v>
@@ -7000,11 +7000,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.1314810578984628</v>
+        <v>0.1343904462458965</v>
       </c>
       <c r="E286" t="n">
         <v>5</v>
@@ -7023,11 +7023,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.1284211301960059</v>
+        <v>0.1220899818297792</v>
       </c>
       <c r="E287" t="n">
         <v>6</v>
@@ -7046,11 +7046,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.1231701979584866</v>
+        <v>0.1152278408648154</v>
       </c>
       <c r="E288" t="n">
         <v>7</v>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.0395463686722311</v>
+        <v>0.02763531234797173</v>
       </c>
       <c r="E289" t="n">
         <v>8</v>
@@ -7092,11 +7092,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.1480683053593875</v>
+        <v>0.1424409720450504</v>
       </c>
       <c r="E290" t="n">
         <v>1</v>
@@ -7115,11 +7115,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.1460047337522556</v>
+        <v>0.1419069142611766</v>
       </c>
       <c r="E291" t="n">
         <v>2</v>
@@ -7138,11 +7138,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.1443853886803048</v>
+        <v>0.1392110342004624</v>
       </c>
       <c r="E292" t="n">
         <v>3</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.1427856537679415</v>
+        <v>0.1357242158679328</v>
       </c>
       <c r="E293" t="n">
         <v>4</v>
@@ -7184,11 +7184,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.1344333402998063</v>
+        <v>0.1349862816736122</v>
       </c>
       <c r="E294" t="n">
         <v>5</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.130919261276947</v>
+        <v>0.1344415814698577</v>
       </c>
       <c r="E295" t="n">
         <v>6</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.1230042782115337</v>
+        <v>0.1334785760147447</v>
       </c>
       <c r="E296" t="n">
         <v>7</v>
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.03039903865182349</v>
+        <v>0.03781042446716331</v>
       </c>
       <c r="E297" t="n">
         <v>8</v>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.1589016105693498</v>
+        <v>0.1535727242355789</v>
       </c>
       <c r="E298" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.1408570148776119</v>
+        <v>0.1507729084006389</v>
       </c>
       <c r="E299" t="n">
         <v>2</v>
@@ -7322,11 +7322,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.138256540155301</v>
+        <v>0.1474076547973672</v>
       </c>
       <c r="E300" t="n">
         <v>3</v>
@@ -7345,11 +7345,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.1369811773176481</v>
+        <v>0.146207772597286</v>
       </c>
       <c r="E301" t="n">
         <v>4</v>
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.1291390401915577</v>
+        <v>0.1295355854792545</v>
       </c>
       <c r="E302" t="n">
         <v>5</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.1289486737167622</v>
+        <v>0.1220348388300107</v>
       </c>
       <c r="E303" t="n">
         <v>6</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.1281412189757882</v>
+        <v>0.1214709715884028</v>
       </c>
       <c r="E304" t="n">
         <v>7</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.03877472419598108</v>
+        <v>0.02899754407146102</v>
       </c>
       <c r="E305" t="n">
         <v>8</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1642596312543621</v>
+        <v>0.1650522394304711</v>
       </c>
       <c r="E306" t="n">
         <v>1</v>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.1420296712441565</v>
+        <v>0.1455036537731277</v>
       </c>
       <c r="E307" t="n">
         <v>2</v>
@@ -7506,11 +7506,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.1418673588038058</v>
+        <v>0.1411777977466087</v>
       </c>
       <c r="E308" t="n">
         <v>3</v>
@@ -7529,11 +7529,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1373272406261233</v>
+        <v>0.1409774842354334</v>
       </c>
       <c r="E309" t="n">
         <v>4</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.1339007012042054</v>
+        <v>0.1351325499667475</v>
       </c>
       <c r="E310" t="n">
         <v>5</v>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.132946853857835</v>
+        <v>0.133370429262469</v>
       </c>
       <c r="E311" t="n">
         <v>6</v>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.1182639142507125</v>
+        <v>0.1136771025512683</v>
       </c>
       <c r="E312" t="n">
         <v>7</v>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.02940462875879933</v>
+        <v>0.02510874303387435</v>
       </c>
       <c r="E313" t="n">
         <v>8</v>
@@ -7644,11 +7644,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.1516358121404803</v>
+        <v>0.1608578546875862</v>
       </c>
       <c r="E314" t="n">
         <v>1</v>
@@ -7667,11 +7667,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.1488510652849881</v>
+        <v>0.1463434573656419</v>
       </c>
       <c r="E315" t="n">
         <v>2</v>
@@ -7690,11 +7690,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.1451771150064687</v>
+        <v>0.1452654028369321</v>
       </c>
       <c r="E316" t="n">
         <v>3</v>
@@ -7713,11 +7713,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0.1448391956957732</v>
+        <v>0.1382354461076776</v>
       </c>
       <c r="E317" t="n">
         <v>4</v>
@@ -7736,11 +7736,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.1312039872619815</v>
+        <v>0.13040043583852</v>
       </c>
       <c r="E318" t="n">
         <v>5</v>
@@ -7763,7 +7763,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.129381579948879</v>
+        <v>0.1290395301675186</v>
       </c>
       <c r="E319" t="n">
         <v>6</v>
@@ -7782,11 +7782,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Conscientiousness</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.1182940298751466</v>
+        <v>0.1269246300620635</v>
       </c>
       <c r="E320" t="n">
         <v>7</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.03061721478628267</v>
+        <v>0.02293324293406004</v>
       </c>
       <c r="E321" t="n">
         <v>8</v>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.1547788099463741</v>
+        <v>0.170288284218379</v>
       </c>
       <c r="E322" t="n">
         <v>1</v>
@@ -7851,11 +7851,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Openness</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.1421526815373338</v>
+        <v>0.1441198047534341</v>
       </c>
       <c r="E323" t="n">
         <v>2</v>
@@ -7874,11 +7874,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Openness</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.141416164460877</v>
+        <v>0.1413960501747568</v>
       </c>
       <c r="E324" t="n">
         <v>3</v>
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>0.1413398204329031</v>
+        <v>0.1370343561179213</v>
       </c>
       <c r="E325" t="n">
         <v>4</v>
@@ -7920,11 +7920,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Extraversion</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.1321972201404311</v>
+        <v>0.1306524351515083</v>
       </c>
       <c r="E326" t="n">
         <v>5</v>
@@ -7943,11 +7943,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>primary_persona</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.131992589696318</v>
+        <v>0.1303185900317808</v>
       </c>
       <c r="E327" t="n">
         <v>6</v>
@@ -7966,11 +7966,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Extraversion</t>
+          <t>current_mood</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.1200133285212516</v>
+        <v>0.115020490427408</v>
       </c>
       <c r="E328" t="n">
         <v>7</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.03610938526451127</v>
+        <v>0.03116998912481183</v>
       </c>
       <c r="E329" t="n">
         <v>8</v>
